--- a/src/test/resources/tutorial/Priority-Student.xlsx
+++ b/src/test/resources/tutorial/Priority-Student.xlsx
@@ -114,7 +114,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="n" s="9">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="C2" t="n" s="12">
         <v>37928.5</v>
@@ -128,7 +128,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="n" s="9">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="C3" t="n" s="12">
         <v>36615.5</v>
